--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.45</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
